--- a/artfynd/A 11741-2024 artfynd.xlsx
+++ b/artfynd/A 11741-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -973,6 +973,103 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134470278</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Norrköping, Norrköping, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>541990</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6498227</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vånga</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11741-2024 artfynd.xlsx
+++ b/artfynd/A 11741-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -771,6 +776,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93255627</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116184015</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93255533</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,8 +1089,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134470278</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>